--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360552</v>
+        <v>128360054</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588531</v>
+        <v>588522</v>
       </c>
       <c r="R11" t="n">
-        <v>6434723</v>
+        <v>6434770</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360054</v>
+        <v>128360552</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588522</v>
+        <v>588531</v>
       </c>
       <c r="R12" t="n">
-        <v>6434770</v>
+        <v>6434723</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360054</v>
+        <v>128360552</v>
       </c>
       <c r="B11" t="n">
         <v>98619</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588522</v>
+        <v>588531</v>
       </c>
       <c r="R11" t="n">
-        <v>6434770</v>
+        <v>6434723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360552</v>
+        <v>128360054</v>
       </c>
       <c r="B12" t="n">
         <v>98619</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588531</v>
+        <v>588522</v>
       </c>
       <c r="R12" t="n">
-        <v>6434723</v>
+        <v>6434770</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360552</v>
+        <v>128360054</v>
       </c>
       <c r="B11" t="n">
         <v>98632</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588531</v>
+        <v>588522</v>
       </c>
       <c r="R11" t="n">
-        <v>6434723</v>
+        <v>6434770</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360054</v>
+        <v>128360552</v>
       </c>
       <c r="B12" t="n">
         <v>98632</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588522</v>
+        <v>588531</v>
       </c>
       <c r="R12" t="n">
-        <v>6434770</v>
+        <v>6434723</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128360199</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128360515</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128360229</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128360137</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128360646</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128360283</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128360424</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>128359975</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128360536</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360054</v>
+        <v>128360552</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588522</v>
+        <v>588531</v>
       </c>
       <c r="R11" t="n">
-        <v>6434770</v>
+        <v>6434723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360552</v>
+        <v>128360054</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588531</v>
+        <v>588522</v>
       </c>
       <c r="R12" t="n">
-        <v>6434723</v>
+        <v>6434770</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
         <v>128360025</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>129097969</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>129097969</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -2528,7 +2528,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129097704</v>
+        <v>129097752</v>
       </c>
       <c r="B19" t="n">
         <v>98710</v>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588556</v>
+        <v>588493</v>
       </c>
       <c r="R19" t="n">
-        <v>6434735</v>
+        <v>6434773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129097752</v>
+        <v>129097704</v>
       </c>
       <c r="B20" t="n">
         <v>98710</v>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588493</v>
+        <v>588556</v>
       </c>
       <c r="R20" t="n">
-        <v>6434773</v>
+        <v>6434735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129097752</v>
+        <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588493</v>
+        <v>588556</v>
       </c>
       <c r="R19" t="n">
-        <v>6434773</v>
+        <v>6434735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129097704</v>
+        <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588556</v>
+        <v>588493</v>
       </c>
       <c r="R20" t="n">
-        <v>6434735</v>
+        <v>6434773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -1998,7 +1998,7 @@
         <v>129097726</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>129097948</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>129097714</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>129097927</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129097704</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
         <v>129097752</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 41271-2025 artfynd.xlsx
+++ b/artfynd/A 41271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128360199</v>
+        <v>129097777</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långgöl, Sm</t>
+          <t>Långgöl SV, Olofsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588514</v>
+        <v>588593</v>
       </c>
       <c r="R2" t="n">
-        <v>6434754</v>
+        <v>6434758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,72 +772,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Julie Goold</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julie Goold</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128360515</v>
+        <v>129097969</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långgöl, Sm</t>
+          <t>A 41271, Olofsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>588539</v>
       </c>
       <c r="R3" t="n">
-        <v>6434756</v>
+        <v>6434751</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,29 +875,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Julie Goold</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julie Goold</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128360229</v>
+        <v>128359975</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -942,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588517</v>
+        <v>588499</v>
       </c>
       <c r="R4" t="n">
-        <v>6434750</v>
+        <v>6434797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128360137</v>
+        <v>128360025</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1052,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588519</v>
+        <v>588514</v>
       </c>
       <c r="R5" t="n">
-        <v>6434754</v>
+        <v>6434772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128360646</v>
+        <v>128360054</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588516</v>
+        <v>588522</v>
       </c>
       <c r="R6" t="n">
-        <v>6434758</v>
+        <v>6434770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128360283</v>
+        <v>128360137</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1272,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588526</v>
+        <v>588519</v>
       </c>
       <c r="R7" t="n">
-        <v>6434746</v>
+        <v>6434754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128360424</v>
+        <v>128360199</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1363,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1382,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588534</v>
+        <v>588514</v>
       </c>
       <c r="R8" t="n">
-        <v>6434747</v>
+        <v>6434754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128359975</v>
+        <v>128360229</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1473,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1492,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588499</v>
+        <v>588517</v>
       </c>
       <c r="R9" t="n">
-        <v>6434797</v>
+        <v>6434750</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128360536</v>
+        <v>128360283</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,12 +1583,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1602,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588554</v>
+        <v>588526</v>
       </c>
       <c r="R10" t="n">
-        <v>6434744</v>
+        <v>6434746</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360552</v>
+        <v>128360424</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588531</v>
+        <v>588534</v>
       </c>
       <c r="R11" t="n">
-        <v>6434723</v>
+        <v>6434747</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360054</v>
+        <v>128360515</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1803,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1822,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588522</v>
+        <v>588539</v>
       </c>
       <c r="R12" t="n">
-        <v>6434770</v>
+        <v>6434756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128360025</v>
+        <v>128360536</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,12 +1913,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1932,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588514</v>
+        <v>588554</v>
       </c>
       <c r="R13" t="n">
-        <v>6434772</v>
+        <v>6434744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129097726</v>
+        <v>128360552</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,10 +2021,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2034,14 +2036,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 41271, Olofsrum, Sm</t>
+          <t>Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588523</v>
+        <v>588531</v>
       </c>
       <c r="R14" t="n">
-        <v>6434754</v>
+        <v>6434723</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,12 +2070,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Julie Goold</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Julie Goold</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129097948</v>
+        <v>128360646</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,10 +2131,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2140,14 +2146,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 41271, Olofsrum, Sm</t>
+          <t>Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588523</v>
+        <v>588516</v>
       </c>
       <c r="R15" t="n">
-        <v>6434752</v>
+        <v>6434758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,12 +2180,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,22 +2201,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Julie Goold</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Julie Goold</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129097714</v>
+        <v>129097704</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,11 +2252,11 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A  41271, Olofsrum, Sm</t>
+          <t>A 41271, Olofsrum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588530</v>
+        <v>588556</v>
       </c>
       <c r="R16" t="n">
         <v>6434735</v>
@@ -2313,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129097927</v>
+        <v>129097714</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,14 +2358,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 41271, Olofsrum, Sm</t>
+          <t>A  41271, Olofsrum, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588563</v>
+        <v>588530</v>
       </c>
       <c r="R17" t="n">
-        <v>6434734</v>
+        <v>6434735</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,46 +2425,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129097969</v>
+        <v>129097726</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2466,13 +2468,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588539</v>
+        <v>588523</v>
       </c>
       <c r="R18" t="n">
-        <v>6434751</v>
+        <v>6434754</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,6 +2512,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2528,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129097704</v>
+        <v>129097752</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588556</v>
+        <v>588493</v>
       </c>
       <c r="R19" t="n">
-        <v>6434735</v>
+        <v>6434773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129097752</v>
+        <v>129097927</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588493</v>
+        <v>588563</v>
       </c>
       <c r="R20" t="n">
-        <v>6434773</v>
+        <v>6434734</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,6 +2740,112 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129097948</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 41271, Olofsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>588523</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6434752</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
